--- a/Team-Data/2014-15/3-9-2014-15.xlsx
+++ b/Team-Data/2014-15/3-9-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,85 +728,85 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F2" t="n">
         <v>13</v>
       </c>
       <c r="G2" t="n">
-        <v>0.794</v>
+        <v>0.79</v>
       </c>
       <c r="H2" t="n">
         <v>48.2</v>
       </c>
       <c r="I2" t="n">
-        <v>38</v>
+        <v>37.7</v>
       </c>
       <c r="J2" t="n">
-        <v>81.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.468</v>
+        <v>0.465</v>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="M2" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.386</v>
+        <v>0.382</v>
       </c>
       <c r="O2" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="P2" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.776</v>
+        <v>0.777</v>
       </c>
       <c r="R2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="S2" t="n">
-        <v>32.3</v>
+        <v>32.5</v>
       </c>
       <c r="T2" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U2" t="n">
-        <v>25.7</v>
+        <v>25.5</v>
       </c>
       <c r="V2" t="n">
         <v>14.4</v>
       </c>
       <c r="W2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X2" t="n">
         <v>4.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z2" t="n">
         <v>17.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>102.8</v>
+        <v>102.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -754,7 +821,7 @@
         <v>25</v>
       </c>
       <c r="AI2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ2" t="n">
         <v>26</v>
@@ -772,10 +839,10 @@
         <v>2</v>
       </c>
       <c r="AO2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AP2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AQ2" t="n">
         <v>4</v>
@@ -784,10 +851,10 @@
         <v>30</v>
       </c>
       <c r="AS2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AT2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU2" t="n">
         <v>2</v>
@@ -796,13 +863,13 @@
         <v>18</v>
       </c>
       <c r="AW2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ2" t="n">
         <v>1</v>
@@ -811,7 +878,7 @@
         <v>16</v>
       </c>
       <c r="BB2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BC2" t="n">
         <v>2</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F3" t="n">
         <v>36</v>
       </c>
       <c r="G3" t="n">
-        <v>0.419</v>
+        <v>0.41</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
@@ -861,7 +928,7 @@
         <v>38.9</v>
       </c>
       <c r="J3" t="n">
-        <v>88.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="K3" t="n">
         <v>0.44</v>
@@ -873,7 +940,7 @@
         <v>24.4</v>
       </c>
       <c r="N3" t="n">
-        <v>0.331</v>
+        <v>0.333</v>
       </c>
       <c r="O3" t="n">
         <v>15.1</v>
@@ -882,19 +949,19 @@
         <v>20</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.755</v>
+        <v>0.753</v>
       </c>
       <c r="R3" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S3" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="T3" t="n">
         <v>44</v>
       </c>
       <c r="U3" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="V3" t="n">
         <v>13.9</v>
@@ -903,13 +970,13 @@
         <v>8</v>
       </c>
       <c r="X3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y3" t="n">
         <v>5.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AA3" t="n">
         <v>18.2</v>
@@ -918,19 +985,19 @@
         <v>100.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1.3</v>
+        <v>-1.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AE3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF3" t="n">
         <v>20</v>
       </c>
       <c r="AG3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH3" t="n">
         <v>10</v>
@@ -951,7 +1018,7 @@
         <v>12</v>
       </c>
       <c r="AN3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO3" t="n">
         <v>28</v>
@@ -960,19 +1027,19 @@
         <v>28</v>
       </c>
       <c r="AQ3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS3" t="n">
         <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV3" t="n">
         <v>10</v>
@@ -987,7 +1054,7 @@
         <v>26</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA3" t="n">
         <v>30</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -1103,16 +1170,16 @@
         <v>-3.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF4" t="n">
         <v>20</v>
       </c>
       <c r="AG4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH4" t="n">
         <v>5</v>
@@ -1136,13 +1203,13 @@
         <v>27</v>
       </c>
       <c r="AO4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>20</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>21</v>
       </c>
       <c r="AR4" t="n">
         <v>23</v>
@@ -1151,7 +1218,7 @@
         <v>18</v>
       </c>
       <c r="AT4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU4" t="n">
         <v>27</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -1207,28 +1274,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E5" t="n">
         <v>28</v>
       </c>
       <c r="F5" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>0.452</v>
+        <v>0.459</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>36</v>
+        <v>36.2</v>
       </c>
       <c r="J5" t="n">
-        <v>84.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.427</v>
+        <v>0.428</v>
       </c>
       <c r="L5" t="n">
         <v>5.8</v>
@@ -1237,7 +1304,7 @@
         <v>18.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.313</v>
+        <v>0.315</v>
       </c>
       <c r="O5" t="n">
         <v>17.1</v>
@@ -1252,40 +1319,40 @@
         <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="T5" t="n">
-        <v>44.1</v>
+        <v>44.2</v>
       </c>
       <c r="U5" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="V5" t="n">
         <v>12</v>
       </c>
       <c r="W5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="X5" t="n">
         <v>5.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AA5" t="n">
         <v>21.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>94.8</v>
+        <v>95.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.9</v>
+        <v>-1.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
@@ -1297,16 +1364,16 @@
         <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI5" t="n">
         <v>26</v>
       </c>
       <c r="AJ5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL5" t="n">
         <v>27</v>
@@ -1315,16 +1382,16 @@
         <v>26</v>
       </c>
       <c r="AN5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO5" t="n">
         <v>13</v>
       </c>
       <c r="AP5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR5" t="n">
         <v>25</v>
@@ -1333,10 +1400,10 @@
         <v>5</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1351,16 +1418,16 @@
         <v>22</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E6" t="n">
         <v>39</v>
       </c>
       <c r="F6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6</v>
+        <v>0.609</v>
       </c>
       <c r="H6" t="n">
         <v>48.5</v>
@@ -1413,19 +1480,19 @@
         <v>0.44</v>
       </c>
       <c r="L6" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="M6" t="n">
         <v>21.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0.353</v>
+        <v>0.352</v>
       </c>
       <c r="O6" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="P6" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="Q6" t="n">
         <v>0.787</v>
@@ -1443,40 +1510,40 @@
         <v>21.6</v>
       </c>
       <c r="V6" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="W6" t="n">
         <v>6.1</v>
       </c>
       <c r="X6" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Y6" t="n">
         <v>5.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.9</v>
+        <v>101.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
         <v>9</v>
       </c>
       <c r="AF6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH6" t="n">
         <v>9</v>
@@ -1509,7 +1576,7 @@
         <v>2</v>
       </c>
       <c r="AR6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AS6" t="n">
         <v>6</v>
@@ -1518,25 +1585,25 @@
         <v>2</v>
       </c>
       <c r="AU6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW6" t="n">
         <v>29</v>
       </c>
       <c r="AX6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ6" t="n">
         <v>2</v>
       </c>
       <c r="BA6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB6" t="n">
         <v>12</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1719,7 @@
         <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF7" t="n">
         <v>9</v>
@@ -1670,7 +1737,7 @@
         <v>23</v>
       </c>
       <c r="AK7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL7" t="n">
         <v>6</v>
@@ -1682,19 +1749,19 @@
         <v>9</v>
       </c>
       <c r="AO7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT7" t="n">
         <v>17</v>
@@ -1706,25 +1773,25 @@
         <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX7" t="n">
         <v>26</v>
       </c>
       <c r="AY7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ7" t="n">
         <v>3</v>
       </c>
       <c r="BA7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E8" t="n">
         <v>41</v>
       </c>
       <c r="F8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G8" t="n">
-        <v>0.641</v>
+        <v>0.631</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
@@ -1771,40 +1838,40 @@
         <v>39.4</v>
       </c>
       <c r="J8" t="n">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K8" t="n">
         <v>0.46</v>
       </c>
       <c r="L8" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="N8" t="n">
         <v>0.35</v>
       </c>
       <c r="O8" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="P8" t="n">
         <v>21.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.761</v>
+        <v>0.762</v>
       </c>
       <c r="R8" t="n">
         <v>10.4</v>
       </c>
       <c r="S8" t="n">
-        <v>31.8</v>
+        <v>31.6</v>
       </c>
       <c r="T8" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U8" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="V8" t="n">
         <v>12.6</v>
@@ -1813,7 +1880,7 @@
         <v>8.4</v>
       </c>
       <c r="X8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y8" t="n">
         <v>3.8</v>
@@ -1825,37 +1892,37 @@
         <v>21.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.5</v>
+        <v>104.4</v>
       </c>
       <c r="AC8" t="n">
         <v>4.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
       </c>
       <c r="AF8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ8" t="n">
         <v>9</v>
       </c>
       <c r="AK8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM8" t="n">
         <v>6</v>
@@ -1864,22 +1931,22 @@
         <v>13</v>
       </c>
       <c r="AO8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP8" t="n">
         <v>23</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR8" t="n">
         <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -1891,7 +1958,7 @@
         <v>9</v>
       </c>
       <c r="AX8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -1900,13 +1967,13 @@
         <v>12</v>
       </c>
       <c r="BA8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB8" t="n">
         <v>4</v>
       </c>
       <c r="BC8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -1935,22 +2002,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F9" t="n">
         <v>41</v>
       </c>
       <c r="G9" t="n">
-        <v>0.359</v>
+        <v>0.349</v>
       </c>
       <c r="H9" t="n">
         <v>48.3</v>
       </c>
       <c r="I9" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J9" t="n">
         <v>86.7</v>
@@ -1968,10 +2035,10 @@
         <v>0.314</v>
       </c>
       <c r="O9" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P9" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="Q9" t="n">
         <v>0.733</v>
@@ -1980,7 +2047,7 @@
         <v>12.2</v>
       </c>
       <c r="S9" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T9" t="n">
         <v>44.7</v>
@@ -1989,7 +2056,7 @@
         <v>21.6</v>
       </c>
       <c r="V9" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W9" t="n">
         <v>7.5</v>
@@ -1998,28 +2065,28 @@
         <v>4.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Z9" t="n">
         <v>22.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>99.8</v>
+        <v>99.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>-4</v>
+        <v>-4.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG9" t="n">
         <v>24</v>
@@ -2043,31 +2110,31 @@
         <v>13</v>
       </c>
       <c r="AN9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ9" t="n">
         <v>24</v>
       </c>
       <c r="AR9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV9" t="n">
         <v>12</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>13</v>
       </c>
       <c r="AW9" t="n">
         <v>17</v>
@@ -2076,7 +2143,7 @@
         <v>16</v>
       </c>
       <c r="AY9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ9" t="n">
         <v>30</v>
@@ -2088,7 +2155,7 @@
         <v>15</v>
       </c>
       <c r="BC9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-1.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2207,7 +2274,7 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
         <v>21</v>
@@ -2216,7 +2283,7 @@
         <v>7</v>
       </c>
       <c r="AK10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL10" t="n">
         <v>10</v>
@@ -2228,7 +2295,7 @@
         <v>20</v>
       </c>
       <c r="AO10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP10" t="n">
         <v>14</v>
@@ -2240,7 +2307,7 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT10" t="n">
         <v>4</v>
@@ -2270,7 +2337,7 @@
         <v>20</v>
       </c>
       <c r="BC10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -2299,37 +2366,37 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F11" t="n">
         <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>0.806</v>
+        <v>0.803</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
       </c>
       <c r="I11" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="J11" t="n">
-        <v>86.8</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.477</v>
+        <v>0.478</v>
       </c>
       <c r="L11" t="n">
         <v>10.7</v>
       </c>
       <c r="M11" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0.392</v>
+        <v>0.391</v>
       </c>
       <c r="O11" t="n">
         <v>16.2</v>
@@ -2338,7 +2405,7 @@
         <v>21.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.768</v>
+        <v>0.767</v>
       </c>
       <c r="R11" t="n">
         <v>10.3</v>
@@ -2347,10 +2414,10 @@
         <v>34.5</v>
       </c>
       <c r="T11" t="n">
-        <v>44.9</v>
+        <v>44.8</v>
       </c>
       <c r="U11" t="n">
-        <v>26.9</v>
+        <v>27.1</v>
       </c>
       <c r="V11" t="n">
         <v>14.7</v>
@@ -2371,13 +2438,13 @@
         <v>19</v>
       </c>
       <c r="AB11" t="n">
-        <v>109.6</v>
+        <v>109.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2410,10 +2477,10 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ11" t="n">
         <v>11</v>
@@ -2437,7 +2504,7 @@
         <v>4</v>
       </c>
       <c r="AX11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY11" t="n">
         <v>2</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F12" t="n">
         <v>20</v>
       </c>
       <c r="G12" t="n">
-        <v>0.677</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J12" t="n">
-        <v>84.40000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="K12" t="n">
         <v>0.439</v>
@@ -2508,25 +2575,25 @@
         <v>11.6</v>
       </c>
       <c r="M12" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0.345</v>
+        <v>0.346</v>
       </c>
       <c r="O12" t="n">
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
       <c r="P12" t="n">
-        <v>24.2</v>
+        <v>24.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.722</v>
+        <v>0.72</v>
       </c>
       <c r="R12" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S12" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T12" t="n">
         <v>43.8</v>
@@ -2544,22 +2611,22 @@
         <v>4.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.2</v>
+        <v>103.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
@@ -2571,13 +2638,13 @@
         <v>4</v>
       </c>
       <c r="AH12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AI12" t="n">
         <v>19</v>
       </c>
       <c r="AJ12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AK12" t="n">
         <v>22</v>
@@ -2589,13 +2656,13 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
         <v>11</v>
       </c>
       <c r="AP12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AQ12" t="n">
         <v>27</v>
@@ -2604,7 +2671,7 @@
         <v>6</v>
       </c>
       <c r="AS12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT12" t="n">
         <v>13</v>
@@ -2619,10 +2686,10 @@
         <v>3</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AZ12" t="n">
         <v>29</v>
@@ -2634,7 +2701,7 @@
         <v>6</v>
       </c>
       <c r="BC12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -2741,31 +2808,31 @@
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE13" t="n">
         <v>17</v>
       </c>
       <c r="AF13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH13" t="n">
         <v>19</v>
       </c>
       <c r="AI13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ13" t="n">
         <v>16</v>
       </c>
       <c r="AK13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM13" t="n">
         <v>18</v>
@@ -2777,13 +2844,13 @@
         <v>19</v>
       </c>
       <c r="AP13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR13" t="n">
         <v>19</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>18</v>
       </c>
       <c r="AS13" t="n">
         <v>4</v>
@@ -2795,7 +2862,7 @@
         <v>18</v>
       </c>
       <c r="AV13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW13" t="n">
         <v>28</v>
@@ -2810,7 +2877,7 @@
         <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB13" t="n">
         <v>24</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E14" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F14" t="n">
         <v>23</v>
       </c>
       <c r="G14" t="n">
-        <v>0.641</v>
+        <v>0.635</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
       </c>
       <c r="I14" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="J14" t="n">
-        <v>83.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K14" t="n">
         <v>0.47</v>
@@ -2872,19 +2939,19 @@
         <v>9.699999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="N14" t="n">
         <v>0.367</v>
       </c>
       <c r="O14" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="P14" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.716</v>
+        <v>0.718</v>
       </c>
       <c r="R14" t="n">
         <v>9.5</v>
@@ -2896,16 +2963,16 @@
         <v>42.4</v>
       </c>
       <c r="U14" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="V14" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="W14" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="n">
         <v>3.2</v>
@@ -2917,16 +2984,16 @@
         <v>21.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>106</v>
+        <v>106.3</v>
       </c>
       <c r="AC14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AD14" t="n">
         <v>6</v>
       </c>
-      <c r="AD14" t="n">
-        <v>4</v>
-      </c>
       <c r="AE14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
@@ -2935,13 +3002,13 @@
         <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI14" t="n">
         <v>4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK14" t="n">
         <v>2</v>
@@ -2956,7 +3023,7 @@
         <v>4</v>
       </c>
       <c r="AO14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AP14" t="n">
         <v>4</v>
@@ -2974,7 +3041,7 @@
         <v>21</v>
       </c>
       <c r="AU14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV14" t="n">
         <v>2</v>
@@ -2989,7 +3056,7 @@
         <v>1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E15" t="n">
         <v>16</v>
       </c>
       <c r="F15" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G15" t="n">
-        <v>0.262</v>
+        <v>0.258</v>
       </c>
       <c r="H15" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>37.7</v>
+        <v>37.5</v>
       </c>
       <c r="J15" t="n">
-        <v>86.3</v>
+        <v>86.2</v>
       </c>
       <c r="K15" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L15" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M15" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="N15" t="n">
-        <v>0.344</v>
+        <v>0.343</v>
       </c>
       <c r="O15" t="n">
-        <v>17.4</v>
+        <v>17.7</v>
       </c>
       <c r="P15" t="n">
-        <v>23.5</v>
+        <v>23.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.741</v>
+        <v>0.743</v>
       </c>
       <c r="R15" t="n">
         <v>11.5</v>
       </c>
       <c r="S15" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T15" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="U15" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V15" t="n">
         <v>12.9</v>
@@ -3087,25 +3154,25 @@
         <v>7.3</v>
       </c>
       <c r="X15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y15" t="n">
         <v>4.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.5</v>
+        <v>99.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.2</v>
+        <v>-6.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3126,13 +3193,13 @@
         <v>5</v>
       </c>
       <c r="AK15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL15" t="n">
         <v>25</v>
       </c>
       <c r="AM15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN15" t="n">
         <v>17</v>
@@ -3141,22 +3208,22 @@
         <v>12</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AT15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV15" t="n">
         <v>5</v>
@@ -3177,7 +3244,7 @@
         <v>23</v>
       </c>
       <c r="BB15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E16" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F16" t="n">
         <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>0.714</v>
+        <v>0.71</v>
       </c>
       <c r="H16" t="n">
         <v>48.7</v>
@@ -3227,10 +3294,10 @@
         <v>38</v>
       </c>
       <c r="J16" t="n">
-        <v>82.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L16" t="n">
         <v>5.1</v>
@@ -3242,22 +3309,22 @@
         <v>0.333</v>
       </c>
       <c r="O16" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="P16" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="Q16" t="n">
         <v>0.774</v>
       </c>
       <c r="R16" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S16" t="n">
         <v>32.4</v>
       </c>
       <c r="T16" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="U16" t="n">
         <v>21.9</v>
@@ -3266,28 +3333,28 @@
         <v>13</v>
       </c>
       <c r="W16" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="X16" t="n">
         <v>4.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB16" t="n">
         <v>99.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3299,13 +3366,13 @@
         <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
         <v>11</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK16" t="n">
         <v>7</v>
@@ -3317,16 +3384,16 @@
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AR16" t="n">
         <v>21</v>
@@ -3359,7 +3426,7 @@
         <v>14</v>
       </c>
       <c r="BB16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC16" t="n">
         <v>8</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -3391,25 +3458,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E17" t="n">
         <v>28</v>
       </c>
       <c r="F17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G17" t="n">
-        <v>0.444</v>
+        <v>0.452</v>
       </c>
       <c r="H17" t="n">
         <v>48.2</v>
       </c>
       <c r="I17" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="J17" t="n">
-        <v>76.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="K17" t="n">
         <v>0.456</v>
@@ -3421,34 +3488,34 @@
         <v>20.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.342</v>
+        <v>0.343</v>
       </c>
       <c r="O17" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="P17" t="n">
-        <v>24.2</v>
+        <v>24</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.746</v>
+        <v>0.744</v>
       </c>
       <c r="R17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="S17" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T17" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="U17" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V17" t="n">
         <v>14.8</v>
       </c>
       <c r="W17" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X17" t="n">
         <v>4.3</v>
@@ -3460,25 +3527,25 @@
         <v>19.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>94.40000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>-2.6</v>
+        <v>-2.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
       </c>
       <c r="AF17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH17" t="n">
         <v>25</v>
@@ -3490,7 +3557,7 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL17" t="n">
         <v>18</v>
@@ -3502,19 +3569,19 @@
         <v>19</v>
       </c>
       <c r="AO17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AR17" t="n">
         <v>29</v>
       </c>
       <c r="AS17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
@@ -3532,13 +3599,13 @@
         <v>23</v>
       </c>
       <c r="AY17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AZ17" t="n">
         <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB17" t="n">
         <v>28</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E18" t="n">
         <v>33</v>
       </c>
       <c r="F18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G18" t="n">
-        <v>0.524</v>
+        <v>0.532</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
@@ -3591,37 +3658,37 @@
         <v>37.4</v>
       </c>
       <c r="J18" t="n">
-        <v>81.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L18" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M18" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="N18" t="n">
-        <v>0.372</v>
+        <v>0.373</v>
       </c>
       <c r="O18" t="n">
-        <v>16</v>
+        <v>15.8</v>
       </c>
       <c r="P18" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R18" t="n">
         <v>10.1</v>
       </c>
       <c r="S18" t="n">
-        <v>31.2</v>
+        <v>31.4</v>
       </c>
       <c r="T18" t="n">
-        <v>41.3</v>
+        <v>41.5</v>
       </c>
       <c r="U18" t="n">
         <v>23.3</v>
@@ -3639,25 +3706,25 @@
         <v>4.7</v>
       </c>
       <c r="Z18" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA18" t="n">
         <v>19.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>97.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AE18" t="n">
         <v>15</v>
       </c>
       <c r="AF18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG18" t="n">
         <v>15</v>
@@ -3666,16 +3733,16 @@
         <v>11</v>
       </c>
       <c r="AI18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ18" t="n">
         <v>25</v>
       </c>
       <c r="AK18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL18" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AM18" t="n">
         <v>25</v>
@@ -3684,7 +3751,7 @@
         <v>3</v>
       </c>
       <c r="AO18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP18" t="n">
         <v>26</v>
@@ -3699,7 +3766,7 @@
         <v>25</v>
       </c>
       <c r="AT18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU18" t="n">
         <v>7</v>
@@ -3717,13 +3784,13 @@
         <v>14</v>
       </c>
       <c r="AZ18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC18" t="n">
         <v>13</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -3755,55 +3822,55 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E19" t="n">
         <v>14</v>
       </c>
       <c r="F19" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G19" t="n">
-        <v>0.226</v>
+        <v>0.23</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J19" t="n">
         <v>84.3</v>
       </c>
       <c r="K19" t="n">
-        <v>0.434</v>
+        <v>0.435</v>
       </c>
       <c r="L19" t="n">
         <v>4.9</v>
       </c>
       <c r="M19" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.33</v>
+        <v>0.331</v>
       </c>
       <c r="O19" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="P19" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.76</v>
+        <v>0.763</v>
       </c>
       <c r="R19" t="n">
         <v>12.2</v>
       </c>
       <c r="S19" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T19" t="n">
-        <v>42.1</v>
+        <v>41.9</v>
       </c>
       <c r="U19" t="n">
         <v>21.9</v>
@@ -3818,7 +3885,7 @@
         <v>3.9</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z19" t="n">
         <v>19.5</v>
@@ -3827,13 +3894,13 @@
         <v>21.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>97.59999999999999</v>
+        <v>98</v>
       </c>
       <c r="AC19" t="n">
         <v>-7.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AE19" t="n">
         <v>28</v>
@@ -3851,7 +3918,7 @@
         <v>22</v>
       </c>
       <c r="AJ19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK19" t="n">
         <v>25</v>
@@ -3872,13 +3939,13 @@
         <v>2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AR19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT19" t="n">
         <v>24</v>
@@ -3905,7 +3972,7 @@
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC19" t="n">
         <v>28</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -3955,49 +4022,49 @@
         <v>37.8</v>
       </c>
       <c r="J20" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="K20" t="n">
-        <v>0.458</v>
+        <v>0.455</v>
       </c>
       <c r="L20" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M20" t="n">
         <v>19.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.36</v>
+        <v>0.356</v>
       </c>
       <c r="O20" t="n">
         <v>17</v>
       </c>
       <c r="P20" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.772</v>
+        <v>0.765</v>
       </c>
       <c r="R20" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="S20" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="T20" t="n">
-        <v>43.3</v>
+        <v>43.7</v>
       </c>
       <c r="U20" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V20" t="n">
-        <v>13.6</v>
+        <v>13.4</v>
       </c>
       <c r="W20" t="n">
         <v>6.8</v>
       </c>
       <c r="X20" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="Y20" t="n">
         <v>5.8</v>
@@ -4006,16 +4073,16 @@
         <v>18.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.59999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE20" t="n">
         <v>14</v>
@@ -4027,55 +4094,55 @@
         <v>14</v>
       </c>
       <c r="AH20" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK20" t="n">
         <v>13</v>
       </c>
-      <c r="AJ20" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK20" t="n">
+      <c r="AL20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AN20" t="n">
         <v>8</v>
       </c>
-      <c r="AL20" t="n">
-        <v>22</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>24</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>6</v>
-      </c>
       <c r="AO20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP20" t="n">
         <v>17</v>
       </c>
       <c r="AQ20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR20" t="n">
         <v>8</v>
       </c>
-      <c r="AR20" t="n">
-        <v>10</v>
-      </c>
       <c r="AS20" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AT20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AU20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV20" t="n">
         <v>7</v>
       </c>
       <c r="AW20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
@@ -4090,7 +4157,7 @@
         <v>16</v>
       </c>
       <c r="BC20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -4119,34 +4186,34 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E21" t="n">
         <v>12</v>
       </c>
       <c r="F21" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G21" t="n">
-        <v>0.194</v>
+        <v>0.197</v>
       </c>
       <c r="H21" t="n">
         <v>48.4</v>
       </c>
       <c r="I21" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="J21" t="n">
-        <v>82.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="K21" t="n">
         <v>0.431</v>
       </c>
       <c r="L21" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M21" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="N21" t="n">
         <v>0.346</v>
@@ -4155,19 +4222,19 @@
         <v>14.4</v>
       </c>
       <c r="P21" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.767</v>
+        <v>0.771</v>
       </c>
       <c r="R21" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S21" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T21" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="U21" t="n">
         <v>21.3</v>
@@ -4176,10 +4243,10 @@
         <v>14.4</v>
       </c>
       <c r="W21" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X21" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y21" t="n">
         <v>4.3</v>
@@ -4191,19 +4258,19 @@
         <v>19.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>92.3</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AC21" t="n">
-        <v>-9</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="AD21" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
       </c>
       <c r="AF21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG21" t="n">
         <v>30</v>
@@ -4212,10 +4279,10 @@
         <v>16</v>
       </c>
       <c r="AI21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK21" t="n">
         <v>26</v>
@@ -4227,7 +4294,7 @@
         <v>21</v>
       </c>
       <c r="AN21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AR21" t="n">
         <v>16</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -4379,22 +4446,22 @@
         <v>2.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF22" t="n">
         <v>12</v>
       </c>
       <c r="AG22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ22" t="n">
         <v>6</v>
@@ -4412,13 +4479,13 @@
         <v>26</v>
       </c>
       <c r="AO22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP22" t="n">
         <v>11</v>
       </c>
       <c r="AQ22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR22" t="n">
         <v>2</v>
@@ -4439,13 +4506,13 @@
         <v>22</v>
       </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA22" t="n">
         <v>17</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -4483,34 +4550,34 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E23" t="n">
         <v>21</v>
       </c>
       <c r="F23" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G23" t="n">
-        <v>0.333</v>
+        <v>0.328</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J23" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L23" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="N23" t="n">
         <v>0.354</v>
@@ -4519,49 +4586,49 @@
         <v>14.2</v>
       </c>
       <c r="P23" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="Q23" t="n">
         <v>0.729</v>
       </c>
       <c r="R23" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T23" t="n">
-        <v>40.9</v>
+        <v>41.2</v>
       </c>
       <c r="U23" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V23" t="n">
         <v>15</v>
       </c>
       <c r="W23" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X23" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA23" t="n">
         <v>18.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.09999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.1</v>
+        <v>-5.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
         <v>25</v>
@@ -4573,10 +4640,10 @@
         <v>26</v>
       </c>
       <c r="AH23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ23" t="n">
         <v>24</v>
@@ -4585,7 +4652,7 @@
         <v>9</v>
       </c>
       <c r="AL23" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AM23" t="n">
         <v>22</v>
@@ -4606,10 +4673,10 @@
         <v>28</v>
       </c>
       <c r="AS23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU23" t="n">
         <v>26</v>
@@ -4624,7 +4691,7 @@
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AZ23" t="n">
         <v>22</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-10.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4779,13 +4846,13 @@
         <v>22</v>
       </c>
       <c r="AP24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS24" t="n">
         <v>26</v>
@@ -4794,7 +4861,7 @@
         <v>20</v>
       </c>
       <c r="AU24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4803,7 +4870,7 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY24" t="n">
         <v>25</v>
@@ -4812,7 +4879,7 @@
         <v>23</v>
       </c>
       <c r="BA24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -4847,34 +4914,34 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E25" t="n">
         <v>33</v>
       </c>
       <c r="F25" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G25" t="n">
-        <v>0.508</v>
+        <v>0.516</v>
       </c>
       <c r="H25" t="n">
         <v>48.6</v>
       </c>
       <c r="I25" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="J25" t="n">
-        <v>86.40000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.455</v>
+        <v>0.457</v>
       </c>
       <c r="L25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>26.1</v>
+        <v>26.3</v>
       </c>
       <c r="N25" t="n">
         <v>0.352</v>
@@ -4892,40 +4959,40 @@
         <v>11</v>
       </c>
       <c r="S25" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="T25" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="U25" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V25" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W25" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="X25" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y25" t="n">
         <v>4</v>
       </c>
       <c r="Z25" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA25" t="n">
         <v>20.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>104.9</v>
+        <v>105.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
         <v>15</v>
@@ -4940,16 +5007,16 @@
         <v>4</v>
       </c>
       <c r="AI25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ25" t="n">
         <v>4</v>
       </c>
       <c r="AK25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AL25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM25" t="n">
         <v>7</v>
@@ -4958,10 +5025,10 @@
         <v>12</v>
       </c>
       <c r="AO25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ25" t="n">
         <v>6</v>
@@ -4976,16 +5043,16 @@
         <v>18</v>
       </c>
       <c r="AU25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY25" t="n">
         <v>5</v>
@@ -5000,7 +5067,7 @@
         <v>3</v>
       </c>
       <c r="BC25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>5</v>
       </c>
       <c r="AD26" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE26" t="n">
         <v>5</v>
@@ -5164,7 +5231,7 @@
         <v>9</v>
       </c>
       <c r="AW26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX26" t="n">
         <v>10</v>
@@ -5173,13 +5240,13 @@
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA26" t="n">
         <v>24</v>
       </c>
       <c r="BB26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC26" t="n">
         <v>4</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -5211,52 +5278,52 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E27" t="n">
         <v>21</v>
       </c>
       <c r="F27" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G27" t="n">
-        <v>0.339</v>
+        <v>0.344</v>
       </c>
       <c r="H27" t="n">
         <v>48.6</v>
       </c>
       <c r="I27" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J27" t="n">
         <v>80.5</v>
       </c>
       <c r="K27" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L27" t="n">
         <v>5.3</v>
       </c>
       <c r="M27" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="N27" t="n">
-        <v>0.333</v>
+        <v>0.331</v>
       </c>
       <c r="O27" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="P27" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.775</v>
+        <v>0.773</v>
       </c>
       <c r="R27" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S27" t="n">
-        <v>33.5</v>
+        <v>33.7</v>
       </c>
       <c r="T27" t="n">
         <v>44.7</v>
@@ -5271,25 +5338,25 @@
         <v>6.5</v>
       </c>
       <c r="X27" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y27" t="n">
         <v>6</v>
       </c>
       <c r="Z27" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.7</v>
+        <v>100.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4.4</v>
+        <v>-4</v>
       </c>
       <c r="AD27" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5301,10 +5368,10 @@
         <v>25</v>
       </c>
       <c r="AH27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ27" t="n">
         <v>28</v>
@@ -5319,7 +5386,7 @@
         <v>28</v>
       </c>
       <c r="AN27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5328,16 +5395,16 @@
         <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AR27" t="n">
         <v>13</v>
       </c>
       <c r="AS27" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AT27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU27" t="n">
         <v>30</v>
@@ -5352,10 +5419,10 @@
         <v>27</v>
       </c>
       <c r="AY27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AZ27" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BA27" t="n">
         <v>1</v>
@@ -5364,7 +5431,7 @@
         <v>14</v>
       </c>
       <c r="BC27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E28" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F28" t="n">
         <v>23</v>
       </c>
       <c r="G28" t="n">
-        <v>0.623</v>
+        <v>0.629</v>
       </c>
       <c r="H28" t="n">
         <v>48.7</v>
@@ -5411,43 +5478,43 @@
         <v>38.2</v>
       </c>
       <c r="J28" t="n">
-        <v>83.8</v>
+        <v>83.5</v>
       </c>
       <c r="K28" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
         <v>22.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.359</v>
+        <v>0.362</v>
       </c>
       <c r="O28" t="n">
         <v>16.7</v>
       </c>
       <c r="P28" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.771</v>
+        <v>0.772</v>
       </c>
       <c r="R28" t="n">
         <v>9.9</v>
       </c>
       <c r="S28" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="T28" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
       <c r="U28" t="n">
         <v>23.9</v>
       </c>
       <c r="V28" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W28" t="n">
         <v>7.8</v>
@@ -5471,10 +5538,10 @@
         <v>4.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="AE28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF28" t="n">
         <v>6</v>
@@ -5489,10 +5556,10 @@
         <v>8</v>
       </c>
       <c r="AJ28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK28" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AL28" t="n">
         <v>11</v>
@@ -5501,40 +5568,40 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO28" t="n">
         <v>18</v>
       </c>
       <c r="AP28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR28" t="n">
         <v>26</v>
       </c>
       <c r="AS28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX28" t="n">
         <v>7</v>
       </c>
       <c r="AY28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ28" t="n">
         <v>10</v>
@@ -5546,7 +5613,7 @@
         <v>11</v>
       </c>
       <c r="BC28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -5653,19 +5720,19 @@
         <v>3.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF29" t="n">
         <v>9</v>
       </c>
       <c r="AG29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI29" t="n">
         <v>9</v>
@@ -5701,25 +5768,25 @@
         <v>27</v>
       </c>
       <c r="AT29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV29" t="n">
         <v>4</v>
       </c>
       <c r="AW29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX29" t="n">
         <v>19</v>
       </c>
       <c r="AY29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA29" t="n">
         <v>11</v>
@@ -5728,7 +5795,7 @@
         <v>5</v>
       </c>
       <c r="BC29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-0.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE30" t="n">
         <v>20</v>
@@ -5850,7 +5917,7 @@
         <v>30</v>
       </c>
       <c r="AI30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ30" t="n">
         <v>29</v>
@@ -5868,10 +5935,10 @@
         <v>18</v>
       </c>
       <c r="AO30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP30" t="n">
         <v>16</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>15</v>
       </c>
       <c r="AQ30" t="n">
         <v>25</v>
@@ -5880,10 +5947,10 @@
         <v>7</v>
       </c>
       <c r="AS30" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU30" t="n">
         <v>28</v>
@@ -5892,13 +5959,13 @@
         <v>26</v>
       </c>
       <c r="AW30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ30" t="n">
         <v>8</v>
@@ -5907,7 +5974,7 @@
         <v>25</v>
       </c>
       <c r="BB30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC30" t="n">
         <v>18</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
@@ -5939,55 +6006,55 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E31" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F31" t="n">
         <v>28</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="H31" t="n">
         <v>48.5</v>
       </c>
       <c r="I31" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="J31" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.465</v>
+        <v>0.464</v>
       </c>
       <c r="L31" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="M31" t="n">
         <v>16.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0.356</v>
+        <v>0.359</v>
       </c>
       <c r="O31" t="n">
-        <v>15.7</v>
+        <v>15.9</v>
       </c>
       <c r="P31" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="R31" t="n">
         <v>10.6</v>
       </c>
       <c r="S31" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="T31" t="n">
-        <v>44.2</v>
+        <v>44.1</v>
       </c>
       <c r="U31" t="n">
         <v>24.1</v>
@@ -5996,28 +6063,28 @@
         <v>15.1</v>
       </c>
       <c r="W31" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X31" t="n">
         <v>4.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z31" t="n">
         <v>21.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB31" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE31" t="n">
         <v>12</v>
@@ -6029,13 +6096,13 @@
         <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK31" t="n">
         <v>4</v>
@@ -6047,46 +6114,46 @@
         <v>27</v>
       </c>
       <c r="AN31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU31" t="n">
         <v>5</v>
       </c>
       <c r="AV31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX31" t="n">
         <v>17</v>
       </c>
       <c r="AY31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB31" t="n">
         <v>19</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-9-2014-15</t>
+          <t>2015-03-09</t>
         </is>
       </c>
     </row>
